--- a/data/chengdu_jinniu_2026_filled.xlsx
+++ b/data/chengdu_jinniu_2026_filled.xlsx
@@ -862,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2718,6 +2718,213 @@
         </is>
       </c>
       <c r="F75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>项目总投资额（一次性CAPEX，含硬件+安装+管沟+备用金）— 能源托管专用</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>本币</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6500000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A5b</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>灯杆总数（柱数）</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A7a</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>钠灯（HPS）灯具数量</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>盏</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A7b</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LED 灯具数量</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>盏</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A7c</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>其它灯具数量（中杆灯/景观灯等）</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>盏</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B1a</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>上一年度电费支出</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B1b</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>前年度电费支出</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B2a</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>上一年度运维支出</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B2b</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>前年度运维支出</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>客户调研得出的节能率（如：一次X% 二次Y%）</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>文本</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>客户期望年度节省额（年节省目标）</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>本币/年</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>预期合同总金额（合同期合计）</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>本币</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2823,7 +3030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4679,6 +4886,213 @@
         </is>
       </c>
       <c r="F75" s="10" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Total project investment (one-time CAPEX, all-in incl. hardware + installation + trenching + contingency) — for 能源托管 only</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Local currency</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6500000</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>A5b</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Total pole count</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Poles (count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>A7a</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>HPS fixture count</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Fixtures (count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>A7b</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>LED fixture count</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Fixtures (count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>A7c</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Other fixture count (high-pole / decorative)</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Fixtures (count)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>B1a</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Last year (Y-1) electricity bill</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>B1b</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Year before (Y-2) electricity bill</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>B2a</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Last year (Y-1) O&amp;M cost</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>B2b</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Year before (Y-2) O&amp;M cost</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Customer-surveyed savings rates (e.g. primary X% secondary Y%)</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Customer expected annual savings target</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>LC/yr</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Expected total contract value (over full term)</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Local currency</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -6210,7 +6624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E64"/>
+  <dimension ref="A1:E76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7948,6 +8362,330 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>project_investment_cny</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Yes (能源托管)</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>cost_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>A5b</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>pole_count</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>A7a</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>existing_fixtures_hps</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>A7b</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>existing_fixtures_led</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>A7c</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>existing_fixtures_other</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>scope</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>B1a</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>annual_electricity_y_minus_1</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Yes (trend)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>cost_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>B1b</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>annual_electricity_y_minus_2</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Yes (trend)</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>cost_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>B2a</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>annual_om_y_minus_1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Yes (trend)</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>cost_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>B2b</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>annual_om_y_minus_2</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Yes (trend)</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>cost_baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>surveyed_savings_rates_text</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>operating_profile</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>G6</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>expected_annual_savings</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Yes (能源托管)</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>financials</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>H5</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>contract_total_value</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Yes (能源托管)</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>contract</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
